--- a/src/test/java/resources/CustomerAPIData.xlsx
+++ b/src/test/java/resources/CustomerAPIData.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB34FC11-4804-48D9-9A4D-93A0C5564FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MdNafisAhmad\eclipse-workspace\DataDrivenAPI\src\test\java\resources\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5024B38-4513-4EC2-A355-84D2A2DE08F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="510" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -458,16 +463,16 @@
     <t>NB</t>
   </si>
   <si>
-    <t>MOTOR PARTS AND ACCCESSORIES, SHIPPER: KIMPEX INC -- DRUMMONDVILLE, QC</t>
+    <t>SAINT-LIBOIRE</t>
+  </si>
+  <si>
+    <t>MOTOR PARTS AND ACCCESSORIES,SHIPPER: KIMPEX INC -- DRUMMONDVILLE, QC</t>
   </si>
   <si>
     <t>FRATE EXPRESS, S/ GREENLINE</t>
   </si>
   <si>
-    <t>SAINT-LIBOIRE</t>
-  </si>
-  <si>
-    <t>BAKERY PRODUCTS, S/ FARINART - ST LIBOIRE, QC</t>
+    <t>BAKERY PRODUCTS , S/ FARINART - ST LIBOIRE, QC</t>
   </si>
 </sst>
 </file>
@@ -1646,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H9">
         <v>3</v>
@@ -1714,7 +1719,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H10">
         <v>3</v>
@@ -1749,7 +1754,7 @@
         <v>450360</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>41</v>
@@ -1910,5 +1915,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>